--- a/data/trans_orig/KIDMED_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R2-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2726</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3874</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1476</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8700</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>13041</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>118483</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>114007</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>120349</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,75%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,06%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>97835</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>93009</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>100233</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>132126</t>
+          <t>96272</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127491</t>
+          <t>91311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134315</t>
+          <t>98747</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>229961</t>
+          <t>214756</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>224481</t>
+          <t>208517</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>233243</t>
+          <t>218169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5261</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10334</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3623</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3764</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5640</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2418</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11484</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12245</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>84619</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>79546</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87786</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>92676</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>89769</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>94659</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>91646</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>95410</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,06%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>88068</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>82224</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>91290</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,98%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>87,74%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>257</t>
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>180744</t>
+          <t>179278</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>174856</t>
+          <t>173376</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184186</t>
+          <t>182663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5540</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>774</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4024</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5105</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6129</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>813</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -1519,74 +1519,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>53985</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>50304</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>55541</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>49315</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>46065</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,97%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>51185</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>46905</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>52010</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>90,18%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>60258</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>56205</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>61942</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,67%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>147</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>109572</t>
+          <t>105170</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105536</t>
+          <t>100511</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111612</t>
+          <t>107041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4762</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1760</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10515</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7507</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3564</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13066</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>12813</t>
+          <t>12467</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>19980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>192551</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>186798</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>195553</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,67%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>208030</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>202471</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>211973</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>96,52%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>207352</t>
+          <t>168935</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202115</t>
+          <t>162902</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>210920</t>
+          <t>172845</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>415383</t>
+          <t>361486</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>407504</t>
+          <t>353973</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>421168</t>
+          <t>366439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3083</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8827</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2492</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6429</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>725</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>142503</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>136759</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>144750</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,88%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,94%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>113017</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>109080</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>114823</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>97,84%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,43%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>155927</t>
+          <t>112771</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149474</t>
+          <t>108654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>158370</t>
+          <t>114741</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>268945</t>
+          <t>255274</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>261621</t>
+          <t>248554</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>272075</t>
+          <t>258524</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3057</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7686</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1191</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4641</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4585</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3234</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8347</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -2548,74 +2548,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>62806</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>58177</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>64962</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>95,36%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>88,33%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>67704</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>64254</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>93,26%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>69160</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>65771</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>70356</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>65797</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>60684</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>68101</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>95,31%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>177</t>
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>133500</t>
+          <t>131967</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>128520</t>
+          <t>127619</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>136229</t>
+          <t>134658</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20747</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>14134</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>29942</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>16554</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>10874</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>24195</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>22841</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32124</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>39395</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30378</t>
+          <t>27556</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53029</t>
+          <t>49615</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>654948</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>645753</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>661561</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>878</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>628577</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>620936</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>634257</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>96,25%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>709527</t>
+          <t>592983</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>700244</t>
+          <t>584887</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>718505</t>
+          <t>599255</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1338104</t>
+          <t>1247931</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1324470</t>
+          <t>1236312</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1347121</t>
+          <t>1258371</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
